--- a/artfynd/A 15557-2026 artfynd.xlsx
+++ b/artfynd/A 15557-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128793749</v>
+        <v>128793817</v>
       </c>
       <c r="B2" t="n">
-        <v>101972</v>
+        <v>110077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221317</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Åkerkant</t>
+          <t>Skogsbryn mot åkermark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128793817</v>
+        <v>128812122</v>
       </c>
       <c r="B3" t="n">
-        <v>109563</v>
+        <v>110077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,14 +817,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brosätter S om, Srm</t>
+          <t>Brosätter SSV om, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602350</v>
+        <v>602229</v>
       </c>
       <c r="R3" t="n">
-        <v>6540831</v>
+        <v>6540880</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128812134</v>
+        <v>128793749</v>
       </c>
       <c r="B4" t="n">
-        <v>101974</v>
+        <v>102418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,14 +924,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brosätter SSV om, Srm</t>
+          <t>Brosätter S om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602229</v>
+        <v>602350</v>
       </c>
       <c r="R4" t="n">
-        <v>6540880</v>
+        <v>6540831</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Skogsbryn mot åkermark</t>
+          <t>Åkerkant</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128812122</v>
+        <v>128812134</v>
       </c>
       <c r="B5" t="n">
-        <v>109565</v>
+        <v>102418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>221317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 15557-2026 artfynd.xlsx
+++ b/artfynd/A 15557-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128793817</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128812122</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128793749</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,8 +1120,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128812134</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>